--- a/wimoor-erp/erp-boot/src/main/resources/template/PurchaseFormContract.xlsx
+++ b/wimoor-erp/erp-boot/src/main/resources/template/PurchaseFormContract.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19935" windowHeight="7785"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="采购合同" sheetId="1" r:id="rId1"/>
@@ -410,7 +410,20 @@
     <definedName name="wattage5699945011">[1]DB!$A$1480:$A$1480</definedName>
     <definedName name="wattage7801668011">[1]DB!$A$1712:$A$1712</definedName>
   </definedNames>
-  <calcPr calcId="144525" concurrentCalc="0"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -573,14 +586,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ \¥* #,##0.00_ ;_ \¥* \-#,##0.00_ ;_ \¥* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -592,57 +605,32 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="仿宋"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="仿宋"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="36"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="仿宋"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="28"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="仿宋"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -662,32 +650,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -698,14 +662,6 @@
       <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -733,6 +689,45 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="等线"/>
@@ -756,7 +751,28 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -771,67 +787,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -843,115 +925,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -979,9 +995,7 @@
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -990,7 +1004,9 @@
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1005,6 +1021,24 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1057,26 +1091,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1094,230 +1110,230 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -2143,7 +2159,7 @@
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
     </row>
-    <row r="9" spans="3:10">
+    <row r="9" spans="3:11">
       <c r="C9" s="2" t="s">
         <v>3</v>
       </c>
@@ -2176,11 +2192,11 @@
       <c r="J10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K10" s="13" t="s">
+      <c r="K10" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="3:8">
+    <row r="12" spans="3:11">
       <c r="C12" s="2" t="s">
         <v>12</v>
       </c>
@@ -2194,7 +2210,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="3:8">
+    <row r="13" spans="3:11">
       <c r="C13" s="2" t="s">
         <v>7</v>
       </c>
@@ -2208,21 +2224,21 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="3:3">
+    <row r="16" spans="3:11">
       <c r="C16" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="17" ht="15" spans="3:11">
-      <c r="C17" s="7"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
     </row>
     <row r="18" spans="3:11">
       <c r="C18" s="1" t="s">
@@ -2243,7 +2259,7 @@
       <c r="H18" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="I18" s="14" t="s">
+      <c r="I18" s="10" t="s">
         <v>24</v>
       </c>
       <c r="J18" s="1" t="s">
@@ -2251,8 +2267,8 @@
       </c>
       <c r="K18" s="1"/>
     </row>
-    <row r="19" spans="3:10">
-      <c r="C19" s="9" t="s">
+    <row r="19" spans="3:11">
+      <c r="C19" s="11" t="s">
         <v>26</v>
       </c>
       <c r="D19" s="2" t="s">
@@ -2270,37 +2286,37 @@
       <c r="H19" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="I19" t="s">
+      <c r="I19" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="20" ht="15" spans="6:9">
+    <row r="20" ht="15" spans="3:11">
       <c r="F20" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G20" s="10"/>
+      <c r="G20" s="12"/>
       <c r="H20" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="I20" s="15"/>
+      <c r="I20" s="13"/>
     </row>
     <row r="21" s="1" customFormat="1" ht="15" spans="3:11">
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11" t="s">
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="I21" s="16"/>
-      <c r="J21" s="11"/>
-      <c r="K21" s="11"/>
-    </row>
-    <row r="24" spans="3:4">
+      <c r="I21" s="15"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="14"/>
+    </row>
+    <row r="24" spans="3:11">
       <c r="C24" s="2" t="s">
         <v>37</v>
       </c>
@@ -2308,53 +2324,53 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="3:3">
+    <row r="26" spans="3:11">
       <c r="C26" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="27" spans="3:4">
-      <c r="C27" s="12">
+    <row r="27" spans="3:11">
+      <c r="C27" s="16">
         <v>1</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="3:4">
-      <c r="C28" s="12">
+    <row r="28" spans="3:11">
+      <c r="C28" s="16">
         <v>2</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="29" spans="3:4">
-      <c r="C29" s="12">
+    <row r="29" spans="3:11">
+      <c r="C29" s="16">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="30" spans="3:4">
-      <c r="C30" s="12">
+    <row r="30" spans="3:11">
+      <c r="C30" s="16">
         <v>4</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="31" spans="3:4">
-      <c r="C31" s="12">
+    <row r="31" spans="3:11">
+      <c r="C31" s="16">
         <v>5</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="32" spans="3:5">
-      <c r="C32" s="12">
+    <row r="32" spans="3:11">
+      <c r="C32" s="16">
         <v>6</v>
       </c>
       <c r="D32" s="2" t="s">
@@ -2364,12 +2380,12 @@
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="5:5">
+    <row r="33" spans="3:9">
       <c r="E33" s="2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="34" spans="5:5">
+    <row r="34" spans="3:9">
       <c r="E34" s="2" t="s">
         <v>48</v>
       </c>
@@ -2430,7 +2446,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="3:8">
+    <row r="41" spans="3:9">
       <c r="C41" s="2" t="s">
         <v>49</v>
       </c>
@@ -2438,7 +2454,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="44" spans="3:8">
+    <row r="44" spans="3:9">
       <c r="C44" s="2" t="s">
         <v>50</v>
       </c>
